--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488037_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488037_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2283</v>
+        <v>3.3531</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0033</v>
+        <v>5.1281</v>
       </c>
       <c r="F2" t="n">
         <v>-1.775</v>
@@ -610,10 +610,10 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3472</v>
+        <v>-1.2224</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.068</v>
+        <v>-0.9432</v>
       </c>
       <c r="U2" t="n">
         <v>-0.2792</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4938</v>
+        <v>0.4677</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5129</v>
+        <v>0.7396</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0191</v>
+        <v>-0.2718</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1549</v>
@@ -766,13 +766,13 @@
         <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4108</v>
+        <v>-0.4369</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1855</v>
+        <v>-0.9589</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="V4" t="n">
         <v>1.4737</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0891</v>
+        <v>0.1172</v>
       </c>
       <c r="E5" t="n">
         <v>-0.0624</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1515</v>
+        <v>0.1796</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3319</v>
@@ -844,13 +844,13 @@
         <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4512</v>
+        <v>-0.4231</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3888</v>
+        <v>-0.3607</v>
       </c>
       <c r="V5" t="n">
         <v>0.674</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0981</v>
+        <v>-0.9401</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0643</v>
+        <v>0.0376</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0338</v>
+        <v>-0.9777</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7391</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.359</v>
+        <v>-0.201</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8408</v>
+        <v>-2.4206</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9853</v>
+        <v>-0.2599</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1445</v>
+        <v>-2.1608</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4638</v>
+        <v>-1.1798</v>
       </c>
       <c r="H8" t="n">
-        <v>1.158</v>
+        <v>-1.285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3059</v>
+        <v>0.1052</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3608</v>
+        <v>1.9763</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3608</v>
+        <v>0.3096</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.6667</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.897</v>
+        <v>-3.1561</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2028</v>
+        <v>-1.5946</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3059</v>
+        <v>-1.5615</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.5947</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-2.9733</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.9645</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9911</v>
+        <v>2.3787</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4017</v>
+        <v>-1.5867</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3816</v>
+        <v>-1.0735</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0201</v>
+        <v>-0.5132</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0704</v>
+        <v>0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0704</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5154</v>
+        <v>-2.4376</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9335</v>
+        <v>-2.189</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5819</v>
+        <v>-0.2486</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1798</v>
+        <v>1.4638</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.285</v>
+        <v>1.158</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1052</v>
+        <v>0.3059</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9763</v>
+        <v>2.3608</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3096</v>
+        <v>2.3608</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6667</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1561</v>
+        <v>-0.897</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5946</v>
+        <v>-1.2028</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5615</v>
+        <v>0.3059</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5947</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6815</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7471</v>
+        <v>-0.5854</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9344</v>
+        <v>-0.4132</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9405</v>
+        <v>0.0704</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8701</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5696</v>
+        <v>-3.0498</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4022</v>
+        <v>-0.9947</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1674</v>
+        <v>-2.0551</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3839</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1769</v>
+        <v>-0.6571</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7488</v>
+        <v>-0.3413</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4281</v>
+        <v>-0.3158</v>
       </c>
       <c r="V10" t="n">
         <v>0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6469</v>
+        <v>-3.9463</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.641</v>
+        <v>-1.8842</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0059</v>
+        <v>-2.062</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3114</v>
@@ -1312,13 +1312,13 @@
         <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3187</v>
+        <v>0.0193</v>
       </c>
       <c r="T11" t="n">
-        <v>0.18</v>
+        <v>-0.0633</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1387</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9313</v>
+        <v>-6.2607</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4624</v>
+        <v>-4.7638</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4689</v>
+        <v>-1.497</v>
       </c>
       <c r="G12" t="n">
         <v>-7.0734</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7962</v>
+        <v>-0.5332</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0942</v>
+        <v>-0.2072</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.298</v>
+        <v>-0.326</v>
       </c>
       <c r="V12" t="n">
         <v>1.5441</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.374000000000001</v>
+        <v>-7.4238</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9249</v>
+        <v>-2.087</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.4491</v>
+        <v>-5.3368</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0402</v>
@@ -1468,13 +1468,13 @@
         <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4507</v>
+        <v>-1.5005</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9343</v>
+        <v>-1.0964</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5163</v>
+        <v>-0.404</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0813</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.7547</v>
+        <v>-22.1307</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.544300000000001</v>
+        <v>-5.920199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.2104</v>
+        <v>-16.2105</v>
       </c>
       <c r="G14" t="n">
         <v>-17.0338</v>
@@ -1546,13 +1546,13 @@
         <v>12.8846</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.3513</v>
+        <v>-7.727299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.165500000000002</v>
+        <v>-5.541700000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1857</v>
+        <v>-2.1856</v>
       </c>
       <c r="V14" t="n">
         <v>3.6214</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4911</v>
+        <v>6.8539</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8704</v>
+        <v>5.2225</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6207</v>
+        <v>1.6314</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4903</v>
+        <v>4.7331</v>
       </c>
       <c r="H15" t="n">
-        <v>4.943</v>
+        <v>1.4134</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4526</v>
+        <v>3.3197</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3883</v>
+        <v>5.1737</v>
       </c>
       <c r="K15" t="n">
-        <v>6.0602</v>
+        <v>1.7353</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6719</v>
+        <v>3.4384</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.898</v>
+        <v>-0.4406</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1172</v>
+        <v>-0.3219</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.1187</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7751</v>
+        <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0712</v>
+        <v>0.7333</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3277</v>
+        <v>0.0488</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7435</v>
+        <v>0.6845</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.4921</v>
+        <v>6.2334</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9169</v>
+        <v>4.4443</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5753</v>
+        <v>1.7891</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7331</v>
+        <v>2.4903</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4134</v>
+        <v>4.943</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3197</v>
+        <v>-2.4526</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1737</v>
+        <v>4.3883</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7353</v>
+        <v>6.0602</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4384</v>
+        <v>-1.6719</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4406</v>
+        <v>-1.898</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3219</v>
+        <v>-1.1172</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1187</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3876</v>
+        <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3715</v>
+        <v>1.8135</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2568</v>
+        <v>0.9015</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6283</v>
+        <v>0.912</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.1617</v>
+        <v>4.7956</v>
       </c>
       <c r="E17" t="n">
-        <v>5.5535</v>
+        <v>4.6367</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6082</v>
+        <v>0.159</v>
       </c>
       <c r="G17" t="n">
         <v>5.1758</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9969</v>
+        <v>1.6308</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5934</v>
+        <v>0.6765</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4035</v>
+        <v>0.9542</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6145</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.303</v>
+        <v>4.2616</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6309</v>
+        <v>3.1403</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6721</v>
+        <v>1.1213</v>
       </c>
       <c r="G18" t="n">
         <v>3.4954</v>
@@ -1858,13 +1858,13 @@
         <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5117</v>
+        <v>0.447</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5688</v>
+        <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0572</v>
+        <v>0.5064</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8701</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9226</v>
+        <v>1.9442</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0172</v>
+        <v>0.6284</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9054</v>
+        <v>1.3157</v>
       </c>
       <c r="G19" t="n">
         <v>3.2703</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2292</v>
+        <v>1.2508</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2568</v>
+        <v>0.3544</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4861</v>
+        <v>0.8964</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6123</v>
+        <v>1.1206</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0411</v>
+        <v>1.6336</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4288</v>
+        <v>-0.513</v>
       </c>
       <c r="G20" t="n">
         <v>1.8361</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9129</v>
+        <v>0.4212</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3586</v>
+        <v>0.2743</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1367</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1569</v>
+        <v>0.8419</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7036</v>
+        <v>-0.9905</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8605</v>
+        <v>1.8325</v>
       </c>
       <c r="G21" t="n">
         <v>0.5861</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1032</v>
+        <v>0.5818</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8112</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.708</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.0704</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5966</v>
+        <v>0.3058</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4395</v>
+        <v>0.9489</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0362</v>
+        <v>-0.6431</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7912</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2035</v>
+        <v>1.1059</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1103</v>
+        <v>0.6197</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0931</v>
+        <v>0.4863</v>
       </c>
       <c r="V22" t="n">
         <v>0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0116</v>
+        <v>-4.0782</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6679</v>
+        <v>-3.5661</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3437</v>
+        <v>-0.5121</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2758</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6695</v>
+        <v>0.6029</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2568</v>
+        <v>-0.155</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9264</v>
+        <v>0.7579</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8107</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>22.5315</v>
+        <v>22.2788</v>
       </c>
       <c r="E24" t="n">
-        <v>16.098</v>
+        <v>16.0981</v>
       </c>
       <c r="F24" t="n">
-        <v>6.4335</v>
+        <v>6.1808</v>
       </c>
       <c r="G24" t="n">
         <v>16.5201</v>
@@ -2326,13 +2326,13 @@
         <v>13.6776</v>
       </c>
       <c r="S24" t="n">
-        <v>8.8398</v>
+        <v>8.587199999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4353</v>
+        <v>2.4352</v>
       </c>
       <c r="U24" t="n">
-        <v>6.404699999999999</v>
+        <v>6.1519</v>
       </c>
       <c r="V24" t="n">
         <v>-3.6213</v>
